--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -782,62 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134375</v>
+        <v>129134748</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521457</v>
+        <v>521528</v>
       </c>
       <c r="R3" t="n">
-        <v>7000903</v>
+        <v>7000725</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +886,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,53 +924,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129134748</v>
+        <v>129134375</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521528</v>
+        <v>521457</v>
       </c>
       <c r="R4" t="n">
-        <v>7000725</v>
+        <v>7000903</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,27 +1032,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98568</v>
+        <v>98573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1401,59 +1401,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R8" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1485,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,11 +1492,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,45 +1508,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R9" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1613,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,42 +2028,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R13" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,14 +2124,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,37 +2155,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R14" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,9 +2261,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129133738</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>129134375</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>129134448</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>129133962</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,45 +1401,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R8" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1471,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1506,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,59 +1527,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B9" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,11 +1618,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>129133310</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129134404</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129134065</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2800,6 +2800,1982 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129193580</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>521261</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7001011</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129193587</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>521477</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7000901</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129193519</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>521485</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7000959</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129193547</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91546</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>521668</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7000768</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129193556</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>521266</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7001005</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129193554</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>521326</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7001045</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129193586</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>521508</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7000887</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129193595</v>
+      </c>
+      <c r="B26" t="n">
+        <v>100847</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>521268</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7000998</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129193555</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>521328</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7000992</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129193521</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>521291</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7000975</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129193522</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>521250</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7001020</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129193551</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>521431</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7001004</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129193520</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>521292</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7000961</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129193577</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>521495</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7000964</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129193572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57827</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>521269</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7000989</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129193594</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100847</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>521395</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7000981</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129193553</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>521328</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7001061</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129193578</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>521452</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7000969</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129193592</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92103</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>760</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>521261</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7000984</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129193552</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>521340</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7001056</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -1401,59 +1401,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R8" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1485,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,11 +1492,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,45 +1508,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R9" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1613,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R29" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,11 +3854,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,21 +3891,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3915,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R30" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,6 +3951,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R2" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +776,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R3" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +908,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R35" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R36" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R2" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,31 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -817,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R3" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +883,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1401,45 +1401,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R8" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1471,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1506,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,59 +1527,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,11 +1618,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,37 +2028,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R13" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,9 +2134,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2144,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,42 +2170,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R14" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,12 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,14 +2266,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R35" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B36" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R36" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R2" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +776,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,53 +817,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134748</v>
+        <v>129134375</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521528</v>
+        <v>521457</v>
       </c>
       <c r="R3" t="n">
-        <v>7000725</v>
+        <v>7000903</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +911,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,27 +925,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,62 +943,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129134375</v>
+        <v>129133738</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521457</v>
+        <v>521324</v>
       </c>
       <c r="R4" t="n">
-        <v>7000903</v>
+        <v>7000946</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,11 +1034,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>129134448</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>129133962</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,59 +1401,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R8" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1485,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,11 +1492,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,45 +1508,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R9" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1613,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,42 +2028,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R13" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,14 +2124,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,37 +2155,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R14" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,9 +2261,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129134878</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129134404</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129134065</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>129193587</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>129193519</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>129193556</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>129193554</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>129193586</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B27" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R27" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,6 +3655,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,21 +3697,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R28" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,11 +3757,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B29" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R29" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,6 +3854,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3891,21 +3896,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3915,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R30" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3951,11 +3956,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3982,32 +3982,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193520</v>
+        <v>129193577</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521292</v>
+        <v>521495</v>
       </c>
       <c r="R31" t="n">
-        <v>7000961</v>
+        <v>7000964</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,11 +4053,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,32 +4079,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193577</v>
+        <v>129193520</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521495</v>
+        <v>521292</v>
       </c>
       <c r="R32" t="n">
-        <v>7000964</v>
+        <v>7000961</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4184,7 +4184,7 @@
         <v>129193572</v>
       </c>
       <c r="B33" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R35" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R36" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B37" t="n">
-        <v>92103</v>
+        <v>80144</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R37" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>92110</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R38" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -1401,45 +1401,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R8" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1471,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1506,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,59 +1527,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,11 +1618,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R2" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,31 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -817,62 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134375</v>
+        <v>129134748</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521457</v>
+        <v>521528</v>
       </c>
       <c r="R3" t="n">
-        <v>7000903</v>
+        <v>7000725</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +886,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,48 +924,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133738</v>
+        <v>129134375</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521324</v>
+        <v>521457</v>
       </c>
       <c r="R4" t="n">
-        <v>7000946</v>
+        <v>7000903</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,6 +1029,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1401,59 +1401,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R8" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1485,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,11 +1492,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,45 +1508,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R9" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1613,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R27" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,11 +3655,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B28" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,21 +3692,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R28" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,6 +3752,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3982,32 +3982,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193577</v>
+        <v>129193520</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521495</v>
+        <v>521292</v>
       </c>
       <c r="R31" t="n">
-        <v>7000964</v>
+        <v>7000961</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,6 +4053,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4079,32 +4084,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193520</v>
+        <v>129193577</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521292</v>
+        <v>521495</v>
       </c>
       <c r="R32" t="n">
-        <v>7000961</v>
+        <v>7000964</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>129193578</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>80144</v>
+        <v>92117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R37" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B38" t="n">
-        <v>92110</v>
+        <v>80144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R38" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R2" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +776,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R3" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +908,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -927,7 +927,7 @@
         <v>129134375</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>129134448</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>129133962</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,45 +1401,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R8" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1471,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1506,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,59 +1527,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,11 +1618,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,37 +2028,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R13" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,9 +2134,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2144,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,42 +2170,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R14" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,12 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,14 +2266,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129134878</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129134404</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129134065</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>129193587</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>129193519</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>129193556</v>
       </c>
       <c r="B23" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>129193554</v>
       </c>
       <c r="B24" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>129193586</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B27" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R27" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,6 +3655,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,21 +3697,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R28" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,11 +3757,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R29" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,11 +3854,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,21 +3891,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3915,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R30" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,6 +3951,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3985,7 +3985,7 @@
         <v>129193520</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>129193577</v>
       </c>
       <c r="B32" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>129193572</v>
       </c>
       <c r="B33" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>129193578</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>129193553</v>
       </c>
       <c r="B36" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B37" t="n">
-        <v>92117</v>
+        <v>80146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R37" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B38" t="n">
-        <v>80144</v>
+        <v>92119</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R38" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R2" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,31 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -817,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R3" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +883,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1401,59 +1401,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R8" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1485,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,11 +1492,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,45 +1508,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R9" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1613,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,42 +2028,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R13" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,14 +2124,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,37 +2155,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R14" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,9 +2261,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R27" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,11 +3655,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,21 +3692,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R28" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,6 +3752,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R35" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R36" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>80146</v>
+        <v>92119</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R37" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B38" t="n">
-        <v>92119</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R38" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,48 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129133738</v>
+        <v>129134375</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521324</v>
+        <v>521457</v>
       </c>
       <c r="R2" t="n">
-        <v>7000946</v>
+        <v>7000903</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +780,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R3" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +892,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,62 +908,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129134375</v>
+        <v>129134748</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521457</v>
+        <v>521528</v>
       </c>
       <c r="R4" t="n">
-        <v>7000903</v>
+        <v>7000725</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1012,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98595</v>
+        <v>98621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1401,45 +1401,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R8" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1471,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1506,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,59 +1527,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,11 +1618,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>129193577</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R35" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B36" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R36" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4588,7 +4588,7 @@
         <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129134375</v>
+        <v>129133738</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521457</v>
+        <v>521324</v>
       </c>
       <c r="R2" t="n">
-        <v>7000903</v>
+        <v>7000946</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R3" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,6 +883,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,53 +924,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129134748</v>
+        <v>129134375</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521528</v>
+        <v>521457</v>
       </c>
       <c r="R4" t="n">
-        <v>7000725</v>
+        <v>7000903</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,27 +1032,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98621</v>
+        <v>98622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1401,59 +1401,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R8" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1485,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,11 +1492,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,45 +1508,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R9" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1613,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R27" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,6 +3655,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,21 +3697,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R28" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,11 +3757,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R29" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,6 +3854,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3891,21 +3896,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3915,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R30" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3951,11 +3956,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4087,7 +4087,7 @@
         <v>129193577</v>
       </c>
       <c r="B32" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B35" t="n">
-        <v>98704</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R35" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>98705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R36" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B37" t="n">
-        <v>92134</v>
+        <v>80146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R37" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>92135</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R38" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R2" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +776,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,53 +817,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134748</v>
+        <v>129134375</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521528</v>
+        <v>521457</v>
       </c>
       <c r="R3" t="n">
-        <v>7000725</v>
+        <v>7000903</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +911,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,27 +925,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,62 +943,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129134375</v>
+        <v>129133738</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521457</v>
+        <v>521324</v>
       </c>
       <c r="R4" t="n">
-        <v>7000903</v>
+        <v>7000946</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,11 +1034,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,37 +2028,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R13" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,9 +2134,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2144,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,42 +2170,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R14" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,12 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,14 +2266,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R27" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,11 +3655,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,21 +3692,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R28" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,6 +3752,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R29" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,11 +3854,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,21 +3891,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3915,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R30" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,6 +3951,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4087,7 +4087,7 @@
         <v>129193577</v>
       </c>
       <c r="B32" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R35" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B36" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R36" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>80146</v>
+        <v>92135</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R37" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B38" t="n">
-        <v>92135</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R38" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R2" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,31 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -817,62 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134375</v>
+        <v>129134748</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521457</v>
+        <v>521528</v>
       </c>
       <c r="R3" t="n">
-        <v>7000903</v>
+        <v>7000725</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +886,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -943,48 +924,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129133738</v>
+        <v>129134375</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521324</v>
+        <v>521457</v>
       </c>
       <c r="R4" t="n">
-        <v>7000946</v>
+        <v>7000903</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,6 +1029,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98623</v>
+        <v>98627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>129134448</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>129133962</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,45 +1401,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R8" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1471,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1506,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,59 +1527,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,11 +1618,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,42 +2028,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R13" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,14 +2124,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,37 +2155,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R14" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,9 +2261,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129134404</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129134065</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>129193587</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>129193556</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>129193554</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>129193586</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>129193555</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>129193551</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193520</v>
+        <v>129193577</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521292</v>
+        <v>521495</v>
       </c>
       <c r="R31" t="n">
-        <v>7000961</v>
+        <v>7000964</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,11 +4053,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,32 +4079,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193577</v>
+        <v>129193520</v>
       </c>
       <c r="B32" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521495</v>
+        <v>521292</v>
       </c>
       <c r="R32" t="n">
-        <v>7000964</v>
+        <v>7000961</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B35" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R35" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R36" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B37" t="n">
-        <v>92135</v>
+        <v>80148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R37" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>92138</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R38" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -3982,32 +3982,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193577</v>
+        <v>129193520</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521495</v>
+        <v>521292</v>
       </c>
       <c r="R31" t="n">
-        <v>7000964</v>
+        <v>7000961</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,6 +4053,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4079,32 +4084,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193520</v>
+        <v>129193577</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521292</v>
+        <v>521495</v>
       </c>
       <c r="R32" t="n">
-        <v>7000961</v>
+        <v>7000964</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>80148</v>
+        <v>92138</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R37" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B38" t="n">
-        <v>92138</v>
+        <v>80148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R38" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129133738</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>129134375</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98627</v>
+        <v>98629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>129134448</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>129133962</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>129134300</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129134710</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,37 +2028,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R13" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,9 +2134,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2144,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,42 +2170,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R14" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,12 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,14 +2266,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129134404</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129134065</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>129193587</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>129193556</v>
       </c>
       <c r="B23" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>129193554</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>129193586</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B27" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R27" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,6 +3655,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,21 +3697,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R28" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,11 +3757,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3786,7 +3786,7 @@
         <v>129193551</v>
       </c>
       <c r="B29" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3982,32 +3982,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193520</v>
+        <v>129193577</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521292</v>
+        <v>521495</v>
       </c>
       <c r="R31" t="n">
-        <v>7000961</v>
+        <v>7000964</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,11 +4053,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,32 +4079,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193577</v>
+        <v>129193520</v>
       </c>
       <c r="B32" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521495</v>
+        <v>521292</v>
       </c>
       <c r="R32" t="n">
-        <v>7000964</v>
+        <v>7000961</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B35" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R35" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B36" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R36" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4588,7 +4588,7 @@
         <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>92138</v>
+        <v>92140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>129193552</v>
       </c>
       <c r="B38" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>129134375</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98629</v>
+        <v>98633</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1401,59 +1401,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R8" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1485,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,11 +1492,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,45 +1508,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R9" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1613,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>129193577</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B35" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R35" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R36" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4588,7 +4588,7 @@
         <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>92140</v>
+        <v>92144</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R2" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +776,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R3" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +908,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -927,7 +927,7 @@
         <v>129134375</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98633</v>
+        <v>98641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,42 +2028,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R13" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,14 +2124,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,37 +2155,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R14" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,9 +2261,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R27" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,11 +3655,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,21 +3692,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R28" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,6 +3752,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R29" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,6 +3854,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3891,21 +3896,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3915,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R30" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3951,11 +3956,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3985,7 +3985,7 @@
         <v>129193577</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R35" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B36" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R36" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4588,7 +4588,7 @@
         <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R2" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,31 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -817,48 +782,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129133738</v>
+        <v>129134375</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521324</v>
+        <v>521457</v>
       </c>
       <c r="R3" t="n">
-        <v>7000946</v>
+        <v>7000903</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +887,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,62 +908,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129134375</v>
+        <v>129134748</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521457</v>
+        <v>521528</v>
       </c>
       <c r="R4" t="n">
-        <v>7000903</v>
+        <v>7000725</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1012,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1401,45 +1401,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R8" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1471,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1506,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,59 +1527,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,11 +1618,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,37 +2028,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R13" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,9 +2134,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2144,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,42 +2170,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R14" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,12 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,14 +2266,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R29" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,11 +3854,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,21 +3891,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3915,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R30" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,6 +3951,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R35" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R36" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,48 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129133738</v>
+        <v>129134375</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521324</v>
+        <v>521457</v>
       </c>
       <c r="R2" t="n">
-        <v>7000946</v>
+        <v>7000903</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +780,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,62 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134375</v>
+        <v>129133738</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521457</v>
+        <v>521324</v>
       </c>
       <c r="R3" t="n">
-        <v>7000903</v>
+        <v>7000946</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,11 +892,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -3982,32 +3982,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193577</v>
+        <v>129193520</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521495</v>
+        <v>521292</v>
       </c>
       <c r="R31" t="n">
-        <v>7000964</v>
+        <v>7000961</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,6 +4053,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4079,32 +4084,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193520</v>
+        <v>129193577</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521292</v>
+        <v>521495</v>
       </c>
       <c r="R32" t="n">
-        <v>7000961</v>
+        <v>7000964</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,62 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129134375</v>
+        <v>129134748</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521457</v>
+        <v>521528</v>
       </c>
       <c r="R2" t="n">
-        <v>7000903</v>
+        <v>7000725</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +779,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -908,53 +924,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129134748</v>
+        <v>129134375</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521528</v>
+        <v>521457</v>
       </c>
       <c r="R4" t="n">
-        <v>7000725</v>
+        <v>7000903</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,27 +1032,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98641</v>
+        <v>98644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1401,59 +1401,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R8" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1485,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,11 +1492,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,45 +1508,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R9" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1613,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R29" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,6 +3854,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3891,21 +3896,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3915,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R30" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3951,11 +3956,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4087,7 +4087,7 @@
         <v>129193577</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>129193578</v>
       </c>
       <c r="B36" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R2" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,31 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -817,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R3" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +883,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1401,45 +1401,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R8" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1471,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1506,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,59 +1527,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,11 +1618,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,42 +2028,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R13" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,14 +2124,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,37 +2155,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R14" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2266,9 +2261,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R27" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,6 +3655,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,21 +3697,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R28" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,11 +3757,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R29" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,11 +3854,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,21 +3891,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3915,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R30" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,6 +3951,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3982,32 +3982,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193520</v>
+        <v>129193577</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521292</v>
+        <v>521495</v>
       </c>
       <c r="R31" t="n">
-        <v>7000961</v>
+        <v>7000964</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,11 +4053,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,32 +4079,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193577</v>
+        <v>129193520</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521495</v>
+        <v>521292</v>
       </c>
       <c r="R32" t="n">
-        <v>7000964</v>
+        <v>7000961</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -1401,59 +1401,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R8" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1485,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,11 +1492,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,45 +1508,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R9" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1613,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R27" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,11 +3655,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,21 +3692,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R28" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,6 +3752,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3982,32 +3982,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193577</v>
+        <v>129193520</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521495</v>
+        <v>521292</v>
       </c>
       <c r="R31" t="n">
-        <v>7000964</v>
+        <v>7000961</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,6 +4053,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4079,32 +4084,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193520</v>
+        <v>129193577</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521292</v>
+        <v>521495</v>
       </c>
       <c r="R32" t="n">
-        <v>7000961</v>
+        <v>7000964</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B37" t="n">
-        <v>92148</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R37" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>92148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R38" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R2" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +776,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R3" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +908,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R29" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,6 +3854,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,10 +3885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3891,21 +3896,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3915,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R30" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3951,11 +3956,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R35" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R36" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>92148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R37" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B38" t="n">
-        <v>92148</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R38" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R2" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,31 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -817,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129133738</v>
+        <v>129134748</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521324</v>
+        <v>521528</v>
       </c>
       <c r="R3" t="n">
-        <v>7000946</v>
+        <v>7000725</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +883,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1401,45 +1401,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R8" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1471,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1506,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,59 +1527,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1607,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,11 +1618,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R27" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,6 +3655,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3681,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3692,21 +3697,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3716,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R28" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,11 +3757,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193522</v>
+        <v>129193551</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521250</v>
+        <v>521431</v>
       </c>
       <c r="R29" t="n">
-        <v>7001020</v>
+        <v>7001004</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,11 +3854,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193551</v>
+        <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3896,21 +3891,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3915,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521431</v>
+        <v>521250</v>
       </c>
       <c r="R30" t="n">
-        <v>7001004</v>
+        <v>7001020</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,6 +3951,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R35" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R36" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B37" t="n">
-        <v>92148</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R37" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>92148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R38" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -675,48 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129133738</v>
+        <v>129134375</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521324</v>
+        <v>521457</v>
       </c>
       <c r="R2" t="n">
-        <v>7000946</v>
+        <v>7000903</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +780,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129134748</v>
+        <v>129133738</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521528</v>
+        <v>521324</v>
       </c>
       <c r="R3" t="n">
-        <v>7000725</v>
+        <v>7000946</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +892,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,62 +908,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129134375</v>
+        <v>129134748</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521457</v>
+        <v>521528</v>
       </c>
       <c r="R4" t="n">
-        <v>7000903</v>
+        <v>7000725</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1012,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
         <v>129133291</v>
       </c>
       <c r="B5" t="n">
-        <v>98644</v>
+        <v>98673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>129134448</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>129133962</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,59 +1401,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134300</v>
+        <v>129134710</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521447</v>
+        <v>521546</v>
       </c>
       <c r="R8" t="n">
-        <v>7000910</v>
+        <v>7000736</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1485,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,11 +1492,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1527,45 +1508,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134710</v>
+        <v>129134300</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521546</v>
+        <v>521447</v>
       </c>
       <c r="R9" t="n">
-        <v>7000736</v>
+        <v>7000910</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1597,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1607,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,6 +1613,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <v>129133869</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>129135048</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>129133611</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133310</v>
+        <v>129133414</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,37 +2028,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521261</v>
+        <v>521262</v>
       </c>
       <c r="R13" t="n">
-        <v>7000999</v>
+        <v>7000948</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2087,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,9 +2134,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2144,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133414</v>
+        <v>129133310</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2155,42 +2170,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521262</v>
+        <v>521261</v>
       </c>
       <c r="R14" t="n">
-        <v>7000948</v>
+        <v>7000999</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,12 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,14 +2266,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
         <v>129134513</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129134878</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129134404</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>129134065</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>129193580</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>129193587</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>129193519</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>129193547</v>
       </c>
       <c r="B22" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>129193556</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>129193554</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>129193586</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>129193595</v>
       </c>
       <c r="B26" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193521</v>
+        <v>129193555</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521291</v>
+        <v>521328</v>
       </c>
       <c r="R27" t="n">
-        <v>7000975</v>
+        <v>7000992</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3655,11 +3655,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3681,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193555</v>
+        <v>129193521</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>57730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,21 +3692,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3721,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521328</v>
+        <v>521291</v>
       </c>
       <c r="R28" t="n">
-        <v>7000992</v>
+        <v>7000975</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,6 +3752,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3786,7 +3786,7 @@
         <v>129193551</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>129193520</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>129193577</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>129193572</v>
       </c>
       <c r="B33" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>129193594</v>
       </c>
       <c r="B34" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R35" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R36" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4585,32 +4585,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193552</v>
+        <v>129193592</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>92176</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521340</v>
+        <v>521261</v>
       </c>
       <c r="R37" t="n">
-        <v>7001056</v>
+        <v>7000984</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4682,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193592</v>
+        <v>129193552</v>
       </c>
       <c r="B38" t="n">
-        <v>92148</v>
+        <v>80175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R38" t="n">
-        <v>7000984</v>
+        <v>7001056</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -4391,32 +4391,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193578</v>
+        <v>129193553</v>
       </c>
       <c r="B35" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521452</v>
+        <v>521328</v>
       </c>
       <c r="R35" t="n">
-        <v>7000969</v>
+        <v>7001061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4488,32 +4488,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129193553</v>
+        <v>129193578</v>
       </c>
       <c r="B36" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521328</v>
+        <v>521452</v>
       </c>
       <c r="R36" t="n">
-        <v>7001061</v>
+        <v>7000969</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>129134748</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>129133414</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129134878</v>
       </c>
       <c r="B16" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>129193519</v>
       </c>
       <c r="B21" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>129193521</v>
       </c>
       <c r="B28" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>129193520</v>
       </c>
       <c r="B31" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>129134748</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>129133414</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129134878</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>129193519</v>
       </c>
       <c r="B21" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>129193521</v>
       </c>
       <c r="B28" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>129193520</v>
       </c>
       <c r="B31" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>129134748</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>129133414</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129134878</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>129193519</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>129193521</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>129193520</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>129134748</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>129133414</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>129134878</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>129193519</v>
       </c>
       <c r="B21" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>129193521</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>129193522</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>129193520</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129134375</v>
+        <v>129193592</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,51 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521457</v>
+        <v>521261</v>
       </c>
       <c r="R2" t="n">
-        <v>7000903</v>
+        <v>7000984</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,21 +743,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,31 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129133738</v>
+        <v>129193547</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521324</v>
+        <v>521668</v>
       </c>
       <c r="R3" t="n">
-        <v>7000946</v>
+        <v>7000768</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,19 +840,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,65 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129134748</v>
+        <v>129133310</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521528</v>
+        <v>521261</v>
       </c>
       <c r="R4" t="n">
-        <v>7000725</v>
+        <v>7000999</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +939,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +949,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +963,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1025,14 +976,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1050,53 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129133291</v>
+        <v>129133738</v>
       </c>
       <c r="B5" t="n">
-        <v>98673</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521243</v>
+        <v>521324</v>
       </c>
       <c r="R5" t="n">
-        <v>7000997</v>
+        <v>7000946</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,11 +1087,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1167,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129134448</v>
+        <v>129133962</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1202,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521522</v>
+        <v>521308</v>
       </c>
       <c r="R6" t="n">
-        <v>7000811</v>
+        <v>7000986</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,26 +1194,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1294,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129133962</v>
+        <v>129134065</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1329,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521308</v>
+        <v>521415</v>
       </c>
       <c r="R7" t="n">
-        <v>7000986</v>
+        <v>7000956</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129134710</v>
+        <v>129134404</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1432,17 +1348,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521546</v>
+        <v>521497</v>
       </c>
       <c r="R8" t="n">
-        <v>7000736</v>
+        <v>7000890</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1397,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,6 +1413,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1508,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129134300</v>
+        <v>129134448</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,51 +1465,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521447</v>
+        <v>521522</v>
       </c>
       <c r="R9" t="n">
-        <v>7000910</v>
+        <v>7000811</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1592,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,6 +1549,21 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1634,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129133869</v>
+        <v>129134710</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,51 +1592,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521335</v>
+        <v>521546</v>
       </c>
       <c r="R10" t="n">
-        <v>7000949</v>
+        <v>7000736</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1718,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1728,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,11 +1672,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1760,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129135048</v>
+        <v>129193586</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,51 +1699,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521502</v>
+        <v>521508</v>
       </c>
       <c r="R11" t="n">
-        <v>7000964</v>
+        <v>7000887</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1842,21 +1756,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1865,31 +1769,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129133611</v>
+        <v>129193587</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,51 +1796,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521248</v>
+        <v>521477</v>
       </c>
       <c r="R12" t="n">
-        <v>7000955</v>
+        <v>7000901</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1968,26 +1853,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 220 plantor och 3 fröställningar inom ca 3 m2 yta intill ett stort flyttblock.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1996,31 +1866,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129133414</v>
+        <v>129193551</v>
       </c>
       <c r="B13" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,42 +1893,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521262</v>
+        <v>521431</v>
       </c>
       <c r="R13" t="n">
-        <v>7000948</v>
+        <v>7001004</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2090,26 +1950,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydligt på stambasen.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2118,51 +1963,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129133310</v>
+        <v>129193552</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,37 +1990,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521261</v>
+        <v>521340</v>
       </c>
       <c r="R14" t="n">
-        <v>7000999</v>
+        <v>7001056</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2227,21 +2047,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2250,98 +2060,64 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129134513</v>
+        <v>129193553</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521541</v>
+        <v>521328</v>
       </c>
       <c r="R15" t="n">
-        <v>7000768</v>
+        <v>7001061</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2368,26 +2144,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 250 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2396,31 +2157,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129134878</v>
+        <v>129193554</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,42 +2184,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521574</v>
+        <v>521326</v>
       </c>
       <c r="R16" t="n">
-        <v>7000711</v>
+        <v>7001045</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2490,26 +2241,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2518,51 +2254,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129134404</v>
+        <v>129193555</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2570,34 +2281,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521497</v>
+        <v>521328</v>
       </c>
       <c r="R17" t="n">
-        <v>7000890</v>
+        <v>7000992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2627,26 +2338,11 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2655,51 +2351,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129134065</v>
+        <v>129193556</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,34 +2378,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
+          <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521415</v>
+        <v>521266</v>
       </c>
       <c r="R18" t="n">
-        <v>7000956</v>
+        <v>7001005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2764,19 +2435,9 @@
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2791,60 +2452,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129193580</v>
+        <v>129132945</v>
       </c>
       <c r="B19" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521261</v>
+        <v>521224</v>
       </c>
       <c r="R19" t="n">
-        <v>7001011</v>
+        <v>7000993</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2871,11 +2537,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2884,26 +2565,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129193587</v>
+        <v>129133414</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,37 +2617,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521477</v>
+        <v>521262</v>
       </c>
       <c r="R20" t="n">
-        <v>7000901</v>
+        <v>7000948</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2968,11 +2679,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, tydligt på stambasen.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2981,26 +2707,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129193519</v>
+        <v>129134748</v>
       </c>
       <c r="B21" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3026,19 +2777,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521485</v>
+        <v>521528</v>
       </c>
       <c r="R21" t="n">
-        <v>7000959</v>
+        <v>7000725</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3065,14 +2821,24 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre, på en smal gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3083,26 +2849,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129193547</v>
+        <v>129134878</v>
       </c>
       <c r="B22" t="n">
-        <v>91602</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3110,37 +2901,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521668</v>
+        <v>521574</v>
       </c>
       <c r="R22" t="n">
-        <v>7000768</v>
+        <v>7000711</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3167,11 +2963,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3180,26 +2991,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129193556</v>
+        <v>129193519</v>
       </c>
       <c r="B23" t="n">
-        <v>80175</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3207,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3231,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521266</v>
+        <v>521485</v>
       </c>
       <c r="R23" t="n">
-        <v>7001005</v>
+        <v>7000959</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3267,6 +3103,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3293,10 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129193554</v>
+        <v>129193520</v>
       </c>
       <c r="B24" t="n">
-        <v>80175</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3304,21 +3145,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3328,10 +3169,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521326</v>
+        <v>521292</v>
       </c>
       <c r="R24" t="n">
-        <v>7001045</v>
+        <v>7000961</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3364,6 +3205,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3390,10 +3236,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129193586</v>
+        <v>129193521</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,21 +3247,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3425,10 +3271,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521508</v>
+        <v>521291</v>
       </c>
       <c r="R25" t="n">
-        <v>7000887</v>
+        <v>7000975</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3461,6 +3307,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3487,32 +3338,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129193595</v>
+        <v>129193522</v>
       </c>
       <c r="B26" t="n">
-        <v>100945</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3522,10 +3373,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521268</v>
+        <v>521250</v>
       </c>
       <c r="R26" t="n">
-        <v>7000998</v>
+        <v>7001020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3558,6 +3409,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3584,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129193555</v>
+        <v>129193572</v>
       </c>
       <c r="B27" t="n">
-        <v>80175</v>
+        <v>58057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,34 +3451,50 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Fisksjölandsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521328</v>
+        <v>521269</v>
       </c>
       <c r="R27" t="n">
-        <v>7000992</v>
+        <v>7000989</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3681,45 +3553,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129193521</v>
+        <v>129133291</v>
       </c>
       <c r="B28" t="n">
-        <v>57740</v>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521291</v>
+        <v>521243</v>
       </c>
       <c r="R28" t="n">
-        <v>7000975</v>
+        <v>7000997</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3749,14 +3626,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3767,64 +3649,83 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129193551</v>
+        <v>129133611</v>
       </c>
       <c r="B29" t="n">
-        <v>80175</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodarna, Gammelbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521431</v>
+        <v>521248</v>
       </c>
       <c r="R29" t="n">
-        <v>7001004</v>
+        <v>7000955</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3851,11 +3752,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 220 plantor och 3 fröställningar inom ca 3 m2 yta intill ett stort flyttblock.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3864,64 +3780,83 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129193522</v>
+        <v>129133869</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521250</v>
+        <v>521335</v>
       </c>
       <c r="R30" t="n">
-        <v>7001020</v>
+        <v>7000949</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3948,14 +3883,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3966,64 +3906,83 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129193520</v>
+        <v>129134300</v>
       </c>
       <c r="B31" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521292</v>
+        <v>521447</v>
       </c>
       <c r="R31" t="n">
-        <v>7000961</v>
+        <v>7000910</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4050,14 +4009,19 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4068,26 +4032,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129193577</v>
+        <v>129134375</v>
       </c>
       <c r="B32" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,20 +4081,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521495</v>
+        <v>521457</v>
       </c>
       <c r="R32" t="n">
-        <v>7000964</v>
+        <v>7000903</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4152,11 +4135,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4165,80 +4158,83 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129193572</v>
+        <v>129134513</v>
       </c>
       <c r="B33" t="n">
-        <v>57834</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521269</v>
+        <v>521541</v>
       </c>
       <c r="R33" t="n">
-        <v>7000989</v>
+        <v>7000768</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4265,11 +4261,26 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 250 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4278,64 +4289,83 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129193594</v>
+        <v>129135048</v>
       </c>
       <c r="B34" t="n">
-        <v>100945</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fisksjölandsbodarna, Jmt</t>
+          <t>Gammelbodbäcken, Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521395</v>
+        <v>521502</v>
       </c>
       <c r="R34" t="n">
-        <v>7000981</v>
+        <v>7000964</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4362,11 +4392,21 @@
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-15</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4375,48 +4415,53 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129193553</v>
+        <v>129193577</v>
       </c>
       <c r="B35" t="n">
-        <v>80175</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4426,10 +4471,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521328</v>
+        <v>521495</v>
       </c>
       <c r="R35" t="n">
-        <v>7001061</v>
+        <v>7000964</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4491,7 +4536,7 @@
         <v>129193578</v>
       </c>
       <c r="B36" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4585,10 +4630,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129193592</v>
+        <v>129193580</v>
       </c>
       <c r="B37" t="n">
-        <v>92176</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4596,21 +4641,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4623,7 +4668,7 @@
         <v>521261</v>
       </c>
       <c r="R37" t="n">
-        <v>7000984</v>
+        <v>7001011</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4682,32 +4727,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129193552</v>
+        <v>129193594</v>
       </c>
       <c r="B38" t="n">
-        <v>80175</v>
+        <v>101325</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,10 +4762,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521340</v>
+        <v>521395</v>
       </c>
       <c r="R38" t="n">
-        <v>7001056</v>
+        <v>7000981</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4776,6 +4821,103 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129193595</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fisksjölandsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>521268</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7000998</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42393-2025 artfynd.xlsx
+++ b/artfynd/A 42393-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193592</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193547</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129133310</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129133738</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129133962</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134065</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134404</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,6 +1618,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134448</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134710</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193586</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193587</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193551</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193552</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193553</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193554</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2364,6 +2444,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193555</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2461,6 +2546,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193556</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129132945</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2745,6 +2840,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129133414</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2887,6 +2987,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134748</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3029,6 +3134,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134878</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3131,6 +3241,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193519</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3233,6 +3348,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193520</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3335,6 +3455,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193521</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3437,6 +3562,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193522</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3550,6 +3680,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193572</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3667,6 +3802,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129133291</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3798,6 +3938,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129133611</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3924,6 +4069,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129133869</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4050,6 +4200,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134300</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4176,6 +4331,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134375</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4307,6 +4467,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134513</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4433,6 +4598,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135048</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4530,6 +4700,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193577</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4627,6 +4802,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193578</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4724,6 +4904,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193580</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4821,6 +5006,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193594</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4918,8 +5108,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193595</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>